--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/2. Metodología Scrum/SPRINTS/SITRAFO_Product_Backlog.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/2. Metodología Scrum/SPRINTS/SITRAFO_Product_Backlog.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
     <col width="1.453125" customWidth="1" style="4" min="1" max="1"/>
@@ -1105,6 +1105,126 @@
       <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Planificada para Sprint 2; desarrollada e integrada en el Sprint 1 (25-sep-2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="29" customHeight="1">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>E4-H3</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Como un cliente, necesito consultar el estado de mi pedido con el número de la orden y un código de seguimiento, sin iniciar sesión, con la finalidad de saber en qué etapa está y cuándo lo recibiré.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>API de seguimiento de pedidos</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Finalizada</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>HU-15 en la ERS-01 (RF-OT-12). API pública /api/publica/v1/seguimiento/. Responsable: Camila Olivares. En el repositorio desde el 16-oct-2026, con 19 pruebas automatizadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="29" customHeight="1">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>E2-H4</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Como un cliente o distribuidor, necesito obtener un precio referencial de uno o más modelos con su cantidad, con la finalidad de evaluar el costo y el plazo antes de pedir una cotización.</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>API del cotizador</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>En Proceso</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>HU-16 en la ERS-01 (RF-COM-18). API pública /api/publica/v1/cotizador/. Responsable: Milko Soto. 24 pruebas automatizadas; probada en Docker, pendiente de subir al repositorio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="29" customHeight="1">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>E6-H2</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Como un proveedor autorizado, necesito consultar los materiales bajo su stock mínimo y la cantidad sugerida de reposición, con la finalidad de preparar los despachos a tiempo.</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>API de disponibilidad de materiales</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Planificada</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>HU-17 en la ERS-01 (RF-INV-09). Historia y criterios: Camila Olivares (20-oct); desarrollo: Benjamín Delgado (21 y 22-oct); pruebas: Milko Soto (23-oct).</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/2. Metodología Scrum/SPRINTS/SITRAFO_Product_Backlog.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/2. Metodología Scrum/SPRINTS/SITRAFO_Product_Backlog.xlsx
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Planificada</t>
+          <t xml:space="preserve">En curso</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>HU-17 en la ERS-01 (RF-INV-09). Historia y criterios: Camila Olivares (20-oct); desarrollo: Benjamín Delgado (21 y 22-oct); pruebas: Milko Soto (23-oct).</t>
+          <t xml:space="preserve">HU-17 en la ERS-01 (RF-INV-09) y CU-REP-08 en el CU-01. Historia y criterios: Camila Olivares (19-oct, ajustados el 22-oct); desarrollo: Benjamín Delgado (21-oct, en el repositorio el 22-oct, con 12 pruebas automatizadas); pruebas manuales: Milko Soto (pendiente).</t>
         </is>
       </c>
     </row>
